--- a/data/GreatLink/Dynamic Secure Portfolio.xlsx
+++ b/data/GreatLink/Dynamic Secure Portfolio.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid263360"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid429957"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,21 +26,96 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>27/02/2026</t>
+  </si>
+  <si>
+    <t>0.952</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>26/02/2026</t>
+  </si>
+  <si>
+    <t>0.951</t>
+  </si>
+  <si>
+    <t>25/02/2026</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>0.949</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>0.950</t>
+  </si>
+  <si>
+    <t>19/02/2026</t>
+  </si>
+  <si>
+    <t>16/02/2026</t>
+  </si>
+  <si>
+    <t>0.948</t>
+  </si>
+  <si>
+    <t>13/02/2026</t>
+  </si>
+  <si>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>0.946</t>
+  </si>
+  <si>
+    <t>11/02/2026</t>
+  </si>
+  <si>
+    <t>0.947</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>0.945</t>
+  </si>
+  <si>
+    <t>05/02/2026</t>
+  </si>
+  <si>
+    <t>0.943</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>0.944</t>
+  </si>
+  <si>
+    <t>03/02/2026</t>
+  </si>
+  <si>
     <t>02/02/2026</t>
   </si>
   <si>
-    <t>0.946</t>
-  </si>
-  <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>30/01/2026</t>
   </si>
   <si>
-    <t>0.945</t>
-  </si>
-  <si>
     <t>29/01/2026</t>
   </si>
   <si>
@@ -56,9 +131,6 @@
     <t>23/01/2026</t>
   </si>
   <si>
-    <t>0.944</t>
-  </si>
-  <si>
     <t>22/01/2026</t>
   </si>
   <si>
@@ -77,15 +149,9 @@
     <t>16/01/2026</t>
   </si>
   <si>
-    <t>0.948</t>
-  </si>
-  <si>
     <t>15/01/2026</t>
   </si>
   <si>
-    <t>0.949</t>
-  </si>
-  <si>
     <t>14/01/2026</t>
   </si>
   <si>
@@ -98,9 +164,6 @@
     <t>09/01/2026</t>
   </si>
   <si>
-    <t>0.947</t>
-  </si>
-  <si>
     <t>08/01/2026</t>
   </si>
   <si>
@@ -110,9 +173,6 @@
     <t>06/01/2026</t>
   </si>
   <si>
-    <t>0.943</t>
-  </si>
-  <si>
     <t>05/01/2026</t>
   </si>
   <si>
@@ -236,9 +296,6 @@
     <t>13/11/2025</t>
   </si>
   <si>
-    <t>0.951</t>
-  </si>
-  <si>
     <t>12/11/2025</t>
   </si>
   <si>
@@ -293,9 +350,6 @@
     <t>23/10/2025</t>
   </si>
   <si>
-    <t>0.952</t>
-  </si>
-  <si>
     <t>22/10/2025</t>
   </si>
   <si>
@@ -303,9 +357,6 @@
   </si>
   <si>
     <t>17/10/2025</t>
-  </si>
-  <si>
-    <t>0.950</t>
   </si>
   <si>
     <t>16/10/2025</t>
@@ -675,7 +726,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -686,7 +737,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -697,7 +748,7 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -705,10 +756,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -716,7 +767,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -727,10 +778,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -738,10 +789,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -749,10 +800,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -760,10 +811,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -771,10 +822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -782,10 +833,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
         <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -793,10 +844,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -804,10 +855,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -815,10 +866,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -826,7 +877,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
@@ -837,10 +888,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -848,10 +899,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -859,10 +910,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -870,10 +921,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -881,10 +932,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -892,10 +943,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -903,10 +954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -914,10 +965,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -925,10 +976,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -936,10 +987,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -947,10 +998,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -958,10 +1009,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -969,10 +1020,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -980,10 +1031,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -994,7 +1045,7 @@
         <v>46</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1002,10 +1053,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1013,10 +1064,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -1024,10 +1075,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1035,10 +1086,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1046,10 +1097,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1057,10 +1108,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B39" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1068,10 +1119,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -1079,10 +1130,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -1090,10 +1141,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -1101,10 +1152,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -1112,10 +1163,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1123,10 +1174,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -1134,10 +1185,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -1145,10 +1196,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
         <v>62</v>
-      </c>
-      <c r="B47" t="s">
-        <v>7</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -1159,7 +1210,7 @@
         <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -1170,7 +1221,7 @@
         <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -1178,10 +1229,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1189,10 +1240,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1200,10 +1251,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B52" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C52" t="s">
         <v>5</v>
@@ -1211,10 +1262,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -1222,10 +1273,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B54" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -1233,10 +1284,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -1244,10 +1295,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -1255,10 +1306,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -1266,10 +1317,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -1277,10 +1328,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -1291,7 +1342,7 @@
         <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -1302,7 +1353,7 @@
         <v>79</v>
       </c>
       <c r="B61" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -1313,7 +1364,7 @@
         <v>80</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -1324,7 +1375,7 @@
         <v>81</v>
       </c>
       <c r="B63" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -1335,7 +1386,7 @@
         <v>82</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1346,7 +1397,7 @@
         <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -1354,10 +1405,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B66" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -1365,10 +1416,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B67" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -1376,10 +1427,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -1387,10 +1438,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B69" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -1398,10 +1449,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -1409,10 +1460,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B71" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -1420,10 +1471,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
@@ -1431,10 +1482,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -1442,10 +1493,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B74" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
@@ -1453,10 +1504,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
@@ -1464,10 +1515,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
@@ -1475,12 +1526,199 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
+        <v>97</v>
+      </c>
+      <c r="B77" t="s">
+        <v>96</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
         <v>98</v>
       </c>
-      <c r="B77" t="s">
-        <v>22</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>99</v>
+      </c>
+      <c r="B79" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>100</v>
+      </c>
+      <c r="B80" t="s">
+        <v>96</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>101</v>
+      </c>
+      <c r="B81" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>102</v>
+      </c>
+      <c r="B82" t="s">
+        <v>103</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>104</v>
+      </c>
+      <c r="B83" t="s">
+        <v>96</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>105</v>
+      </c>
+      <c r="B84" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>106</v>
+      </c>
+      <c r="B85" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>107</v>
+      </c>
+      <c r="B86" t="s">
+        <v>103</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>108</v>
+      </c>
+      <c r="B87" t="s">
+        <v>103</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>109</v>
+      </c>
+      <c r="B88" t="s">
+        <v>96</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>110</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>111</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>112</v>
+      </c>
+      <c r="B91" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>113</v>
+      </c>
+      <c r="B92" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>114</v>
+      </c>
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>115</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" t="s">
         <v>5</v>
       </c>
     </row>

--- a/data/GreatLink/Dynamic Secure Portfolio.xlsx
+++ b/data/GreatLink/Dynamic Secure Portfolio.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="PriceHistory" sheetId="1" r:id="GemRid429957"/>
+    <sheet name="PriceHistory" sheetId="1" r:id="GemRid234723"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="155">
   <si>
     <t>Price Date</t>
   </si>
@@ -26,15 +26,156 @@
     <t>Currency - Unit Level</t>
   </si>
   <si>
+    <t>09/04/2026</t>
+  </si>
+  <si>
+    <t>0.940</t>
+  </si>
+  <si>
+    <t>SGD</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>0.932</t>
+  </si>
+  <si>
+    <t>06/04/2026</t>
+  </si>
+  <si>
+    <t>0.931</t>
+  </si>
+  <si>
+    <t>02/04/2026</t>
+  </si>
+  <si>
+    <t>0.930</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>0.927</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>0.921</t>
+  </si>
+  <si>
+    <t>27/03/2026</t>
+  </si>
+  <si>
+    <t>26/03/2026</t>
+  </si>
+  <si>
+    <t>0.925</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>0.928</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>0.926</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>19/03/2026</t>
+  </si>
+  <si>
+    <t>0.933</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>0.937</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>16/03/2026</t>
+  </si>
+  <si>
+    <t>0.936</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>0.935</t>
+  </si>
+  <si>
+    <t>12/03/2026</t>
+  </si>
+  <si>
+    <t>0.938</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>0.941</t>
+  </si>
+  <si>
+    <t>09/03/2026</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>0.944</t>
+  </si>
+  <si>
+    <t>05/03/2026</t>
+  </si>
+  <si>
+    <t>0.946</t>
+  </si>
+  <si>
+    <t>04/03/2026</t>
+  </si>
+  <si>
+    <t>0.947</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>0.953</t>
+  </si>
+  <si>
     <t>27/02/2026</t>
   </si>
   <si>
     <t>0.952</t>
   </si>
   <si>
-    <t>SGD</t>
-  </si>
-  <si>
     <t>26/02/2026</t>
   </si>
   <si>
@@ -74,15 +215,9 @@
     <t>12/02/2026</t>
   </si>
   <si>
-    <t>0.946</t>
-  </si>
-  <si>
     <t>11/02/2026</t>
   </si>
   <si>
-    <t>0.947</t>
-  </si>
-  <si>
     <t>10/02/2026</t>
   </si>
   <si>
@@ -104,9 +239,6 @@
     <t>04/02/2026</t>
   </si>
   <si>
-    <t>0.944</t>
-  </si>
-  <si>
     <t>03/02/2026</t>
   </si>
   <si>
@@ -191,9 +323,6 @@
     <t>26/12/2025</t>
   </si>
   <si>
-    <t>0.941</t>
-  </si>
-  <si>
     <t>24/12/2025</t>
   </si>
   <si>
@@ -203,24 +332,15 @@
     <t>22/12/2025</t>
   </si>
   <si>
-    <t>0.940</t>
-  </si>
-  <si>
     <t>19/12/2025</t>
   </si>
   <si>
     <t>18/12/2025</t>
   </si>
   <si>
-    <t>0.938</t>
-  </si>
-  <si>
     <t>17/12/2025</t>
   </si>
   <si>
-    <t>0.937</t>
-  </si>
-  <si>
     <t>16/12/2025</t>
   </si>
   <si>
@@ -303,9 +423,6 @@
   </si>
   <si>
     <t>11/11/2025</t>
-  </si>
-  <si>
-    <t>0.953</t>
   </si>
   <si>
     <t>10/11/2025</t>
@@ -715,7 +832,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -723,10 +840,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -737,7 +854,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -745,10 +862,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -756,10 +873,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
@@ -770,7 +887,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
@@ -778,10 +895,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -789,10 +906,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
         <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -800,10 +917,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
@@ -811,10 +928,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -825,7 +942,7 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
@@ -833,10 +950,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -844,10 +961,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
@@ -855,10 +972,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
@@ -866,10 +983,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
@@ -877,10 +994,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s">
         <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>27</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
@@ -888,10 +1005,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
@@ -899,10 +1016,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -910,10 +1027,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
@@ -921,10 +1038,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
@@ -932,10 +1049,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -943,10 +1060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
@@ -954,10 +1071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
@@ -965,10 +1082,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
@@ -976,10 +1093,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
@@ -987,10 +1104,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
@@ -998,10 +1115,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
@@ -1009,10 +1126,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
@@ -1020,10 +1137,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
@@ -1031,10 +1148,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
@@ -1042,10 +1159,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
@@ -1053,10 +1170,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
         <v>5</v>
@@ -1064,10 +1181,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="C35" t="s">
         <v>5</v>
@@ -1075,10 +1192,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C36" t="s">
         <v>5</v>
@@ -1086,10 +1203,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="C37" t="s">
         <v>5</v>
@@ -1097,10 +1214,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="C38" t="s">
         <v>5</v>
@@ -1108,10 +1225,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C39" t="s">
         <v>5</v>
@@ -1119,10 +1236,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
         <v>5</v>
@@ -1130,10 +1247,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C41" t="s">
         <v>5</v>
@@ -1141,10 +1258,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -1152,10 +1269,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C43" t="s">
         <v>5</v>
@@ -1163,10 +1280,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C44" t="s">
         <v>5</v>
@@ -1174,10 +1291,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -1185,10 +1302,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C46" t="s">
         <v>5</v>
@@ -1196,10 +1313,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C47" t="s">
         <v>5</v>
@@ -1207,10 +1324,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C48" t="s">
         <v>5</v>
@@ -1218,10 +1335,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C49" t="s">
         <v>5</v>
@@ -1229,10 +1346,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C50" t="s">
         <v>5</v>
@@ -1240,10 +1357,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B51" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C51" t="s">
         <v>5</v>
@@ -1251,7 +1368,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B52" t="s">
         <v>70</v>
@@ -1262,10 +1379,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B53" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="C53" t="s">
         <v>5</v>
@@ -1273,10 +1390,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B54" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C54" t="s">
         <v>5</v>
@@ -1284,10 +1401,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C55" t="s">
         <v>5</v>
@@ -1295,10 +1412,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -1306,10 +1423,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -1317,10 +1434,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
@@ -1328,10 +1445,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C59" t="s">
         <v>5</v>
@@ -1339,10 +1456,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -1350,10 +1467,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="B61" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="C61" t="s">
         <v>5</v>
@@ -1361,10 +1478,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="C62" t="s">
         <v>5</v>
@@ -1372,10 +1489,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
@@ -1383,10 +1500,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1394,10 +1511,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B65" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
@@ -1405,10 +1522,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="B66" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
         <v>5</v>
@@ -1416,10 +1533,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C67" t="s">
         <v>5</v>
@@ -1427,10 +1544,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B68" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="C68" t="s">
         <v>5</v>
@@ -1438,10 +1555,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="C69" t="s">
         <v>5</v>
@@ -1449,10 +1566,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="C70" t="s">
         <v>5</v>
@@ -1460,10 +1577,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="C71" t="s">
         <v>5</v>
@@ -1471,10 +1588,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C72" t="s">
         <v>5</v>
@@ -1482,10 +1599,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C73" t="s">
         <v>5</v>
@@ -1493,10 +1610,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="B74" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C74" t="s">
         <v>5</v>
@@ -1504,10 +1621,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="C75" t="s">
         <v>5</v>
@@ -1515,10 +1632,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="C76" t="s">
         <v>5</v>
@@ -1526,10 +1643,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
       <c r="C77" t="s">
         <v>5</v>
@@ -1537,10 +1654,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B78" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C78" t="s">
         <v>5</v>
@@ -1548,10 +1665,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B79" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="C79" t="s">
         <v>5</v>
@@ -1559,10 +1676,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C80" t="s">
         <v>5</v>
@@ -1570,10 +1687,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="C81" t="s">
         <v>5</v>
@@ -1581,10 +1698,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="C82" t="s">
         <v>5</v>
@@ -1592,10 +1709,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C83" t="s">
         <v>5</v>
@@ -1603,10 +1720,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C84" t="s">
         <v>5</v>
@@ -1614,10 +1731,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="C85" t="s">
         <v>5</v>
@@ -1625,10 +1742,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B86" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C86" t="s">
         <v>5</v>
@@ -1636,10 +1753,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B87" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="C87" t="s">
         <v>5</v>
@@ -1647,10 +1764,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C88" t="s">
         <v>5</v>
@@ -1658,10 +1775,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="B89" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="C89" t="s">
         <v>5</v>
@@ -1669,10 +1786,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B90" t="s">
-        <v>4</v>
+        <v>72</v>
       </c>
       <c r="C90" t="s">
         <v>5</v>
@@ -1680,10 +1797,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="C91" t="s">
         <v>5</v>
@@ -1691,10 +1808,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C92" t="s">
         <v>5</v>
@@ -1702,10 +1819,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B93" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="C93" t="s">
         <v>5</v>
@@ -1713,12 +1830,320 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B94" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>125</v>
+      </c>
+      <c r="B95" t="s">
+        <v>70</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>126</v>
+      </c>
+      <c r="B96" t="s">
+        <v>43</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>127</v>
+      </c>
+      <c r="B97" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>128</v>
+      </c>
+      <c r="B98" t="s">
+        <v>45</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>129</v>
+      </c>
+      <c r="B99" t="s">
+        <v>70</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>130</v>
+      </c>
+      <c r="B100" t="s">
+        <v>63</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>131</v>
+      </c>
+      <c r="B101" t="s">
+        <v>63</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>132</v>
+      </c>
+      <c r="B102" t="s">
+        <v>54</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>133</v>
+      </c>
+      <c r="B103" t="s">
+        <v>134</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>135</v>
+      </c>
+      <c r="B104" t="s">
+        <v>50</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>136</v>
+      </c>
+      <c r="B105" t="s">
+        <v>50</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>137</v>
+      </c>
+      <c r="B106" t="s">
+        <v>58</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>138</v>
+      </c>
+      <c r="B107" t="s">
+        <v>54</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>139</v>
+      </c>
+      <c r="B108" t="s">
+        <v>50</v>
+      </c>
+      <c r="C108" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>140</v>
+      </c>
+      <c r="B109" t="s">
+        <v>50</v>
+      </c>
+      <c r="C109" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>141</v>
+      </c>
+      <c r="B110" t="s">
+        <v>142</v>
+      </c>
+      <c r="C110" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>143</v>
+      </c>
+      <c r="B111" t="s">
+        <v>50</v>
+      </c>
+      <c r="C111" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>144</v>
+      </c>
+      <c r="B112" t="s">
+        <v>50</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>145</v>
+      </c>
+      <c r="B113" t="s">
+        <v>134</v>
+      </c>
+      <c r="C113" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>146</v>
+      </c>
+      <c r="B114" t="s">
+        <v>142</v>
+      </c>
+      <c r="C114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>147</v>
+      </c>
+      <c r="B115" t="s">
+        <v>142</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>148</v>
+      </c>
+      <c r="B116" t="s">
+        <v>50</v>
+      </c>
+      <c r="C116" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>149</v>
+      </c>
+      <c r="B117" t="s">
+        <v>52</v>
+      </c>
+      <c r="C117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>150</v>
+      </c>
+      <c r="B118" t="s">
+        <v>52</v>
+      </c>
+      <c r="C118" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>151</v>
+      </c>
+      <c r="B119" t="s">
+        <v>54</v>
+      </c>
+      <c r="C119" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>152</v>
+      </c>
+      <c r="B120" t="s">
+        <v>60</v>
+      </c>
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>153</v>
+      </c>
+      <c r="B121" t="s">
+        <v>58</v>
+      </c>
+      <c r="C121" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>154</v>
+      </c>
+      <c r="B122" t="s">
+        <v>58</v>
+      </c>
+      <c r="C122" t="s">
         <v>5</v>
       </c>
     </row>
